--- a/reports/Debug-snowbowl-20260105/Month to Date (Prior Year)_Payroll_history.xlsx
+++ b/reports/Debug-snowbowl-20260105/Month to Date (Prior Year)_Payroll_history.xlsx
@@ -22,6 +22,21 @@
     <t>D8030</t>
   </si>
   <si>
+    <t>D1020</t>
+  </si>
+  <si>
+    <t>D1060</t>
+  </si>
+  <si>
+    <t>D1070</t>
+  </si>
+  <si>
+    <t>D5820</t>
+  </si>
+  <si>
+    <t>D9007</t>
+  </si>
+  <si>
     <t>D1000</t>
   </si>
   <si>
@@ -37,19 +52,76 @@
     <t>D7010</t>
   </si>
   <si>
-    <t>D1020</t>
-  </si>
-  <si>
-    <t>D1060</t>
-  </si>
-  <si>
-    <t>D1070</t>
-  </si>
-  <si>
-    <t>D5820</t>
-  </si>
-  <si>
-    <t>D9007</t>
+    <t>D2000</t>
+  </si>
+  <si>
+    <t>D4034</t>
+  </si>
+  <si>
+    <t>D8010</t>
+  </si>
+  <si>
+    <t>D8020</t>
+  </si>
+  <si>
+    <t>D1100</t>
+  </si>
+  <si>
+    <t>D3000</t>
+  </si>
+  <si>
+    <t>D5000</t>
+  </si>
+  <si>
+    <t>D5112</t>
+  </si>
+  <si>
+    <t>D6760</t>
+  </si>
+  <si>
+    <t>D6780</t>
+  </si>
+  <si>
+    <t>D8040</t>
+  </si>
+  <si>
+    <t>D1200</t>
+  </si>
+  <si>
+    <t>D5111</t>
+  </si>
+  <si>
+    <t>D6215</t>
+  </si>
+  <si>
+    <t>D8050</t>
+  </si>
+  <si>
+    <t>D8060</t>
+  </si>
+  <si>
+    <t>D1030</t>
+  </si>
+  <si>
+    <t>D3050</t>
+  </si>
+  <si>
+    <t>D4031</t>
+  </si>
+  <si>
+    <t>D5110</t>
+  </si>
+  <si>
+    <t>D5113</t>
+  </si>
+  <si>
+    <t>D6030</t>
+  </si>
+  <si>
+    <t>D6740</t>
+  </si>
+  <si>
+    <t>D6781</t>
   </si>
   <si>
     <t>D1010</t>
@@ -62,78 +134,6 @@
   </si>
   <si>
     <t>D6790</t>
-  </si>
-  <si>
-    <t>D1100</t>
-  </si>
-  <si>
-    <t>D3000</t>
-  </si>
-  <si>
-    <t>D5000</t>
-  </si>
-  <si>
-    <t>D5112</t>
-  </si>
-  <si>
-    <t>D6760</t>
-  </si>
-  <si>
-    <t>D6780</t>
-  </si>
-  <si>
-    <t>D8040</t>
-  </si>
-  <si>
-    <t>D1200</t>
-  </si>
-  <si>
-    <t>D5111</t>
-  </si>
-  <si>
-    <t>D6215</t>
-  </si>
-  <si>
-    <t>D8050</t>
-  </si>
-  <si>
-    <t>D8060</t>
-  </si>
-  <si>
-    <t>D2000</t>
-  </si>
-  <si>
-    <t>D4034</t>
-  </si>
-  <si>
-    <t>D8010</t>
-  </si>
-  <si>
-    <t>D8020</t>
-  </si>
-  <si>
-    <t>D1030</t>
-  </si>
-  <si>
-    <t>D3050</t>
-  </si>
-  <si>
-    <t>D4031</t>
-  </si>
-  <si>
-    <t>D5110</t>
-  </si>
-  <si>
-    <t>D5113</t>
-  </si>
-  <si>
-    <t>D6030</t>
-  </si>
-  <si>
-    <t>D6740</t>
-  </si>
-  <si>
-    <t>D6781</t>
   </si>
   <si>
     <t>total</t>
@@ -527,7 +527,7 @@
         <v>2</v>
       </c>
       <c r="B3" s="2">
-        <v>4486.35</v>
+        <v>6736.91</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -535,7 +535,7 @@
         <v>3</v>
       </c>
       <c r="B4" s="2">
-        <v>2969.46</v>
+        <v>2937.45</v>
       </c>
     </row>
     <row r="5" spans="1:2">
@@ -543,7 +543,7 @@
         <v>4</v>
       </c>
       <c r="B5" s="2">
-        <v>1042.90</v>
+        <v>4778.02</v>
       </c>
     </row>
     <row r="6" spans="1:2">
@@ -551,7 +551,7 @@
         <v>5</v>
       </c>
       <c r="B6" s="2">
-        <v>4174.55</v>
+        <v>198.90</v>
       </c>
     </row>
     <row r="7" spans="1:2">
@@ -559,7 +559,7 @@
         <v>6</v>
       </c>
       <c r="B7" s="2">
-        <v>2034.41</v>
+        <v>208.97</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -567,7 +567,7 @@
         <v>7</v>
       </c>
       <c r="B8" s="2">
-        <v>6736.91</v>
+        <v>4486.35</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -575,7 +575,7 @@
         <v>8</v>
       </c>
       <c r="B9" s="2">
-        <v>2937.45</v>
+        <v>2969.46</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -583,7 +583,7 @@
         <v>9</v>
       </c>
       <c r="B10" s="2">
-        <v>4778.02</v>
+        <v>1042.90</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -591,7 +591,7 @@
         <v>10</v>
       </c>
       <c r="B11" s="2">
-        <v>198.90</v>
+        <v>4174.55</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -599,7 +599,7 @@
         <v>11</v>
       </c>
       <c r="B12" s="2">
-        <v>208.97</v>
+        <v>2034.41</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -607,7 +607,7 @@
         <v>12</v>
       </c>
       <c r="B13" s="2">
-        <v>30848.02</v>
+        <v>96679.41</v>
       </c>
     </row>
     <row r="14" spans="1:2">
@@ -615,7 +615,7 @@
         <v>13</v>
       </c>
       <c r="B14" s="2">
-        <v>11696.88</v>
+        <v>1474.61</v>
       </c>
     </row>
     <row r="15" spans="1:2">
@@ -623,7 +623,7 @@
         <v>14</v>
       </c>
       <c r="B15" s="2">
-        <v>3328.39</v>
+        <v>4655.20</v>
       </c>
     </row>
     <row r="16" spans="1:2">
@@ -631,7 +631,7 @@
         <v>15</v>
       </c>
       <c r="B16" s="2">
-        <v>2886.37</v>
+        <v>3619.10</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -735,7 +735,7 @@
         <v>28</v>
       </c>
       <c r="B29" s="2">
-        <v>96679.41</v>
+        <v>11169.52</v>
       </c>
     </row>
     <row r="30" spans="1:2">
@@ -743,7 +743,7 @@
         <v>29</v>
       </c>
       <c r="B30" s="2">
-        <v>1474.61</v>
+        <v>1632.97</v>
       </c>
     </row>
     <row r="31" spans="1:2">
@@ -751,7 +751,7 @@
         <v>30</v>
       </c>
       <c r="B31" s="2">
-        <v>4655.20</v>
+        <v>880.65</v>
       </c>
     </row>
     <row r="32" spans="1:2">
@@ -759,7 +759,7 @@
         <v>31</v>
       </c>
       <c r="B32" s="2">
-        <v>3619.10</v>
+        <v>8143.07</v>
       </c>
     </row>
     <row r="33" spans="1:2">
@@ -767,7 +767,7 @@
         <v>32</v>
       </c>
       <c r="B33" s="2">
-        <v>11169.52</v>
+        <v>1149.80</v>
       </c>
     </row>
     <row r="34" spans="1:2">
@@ -775,7 +775,7 @@
         <v>33</v>
       </c>
       <c r="B34" s="2">
-        <v>1632.97</v>
+        <v>2815.05</v>
       </c>
     </row>
     <row r="35" spans="1:2">
@@ -783,7 +783,7 @@
         <v>34</v>
       </c>
       <c r="B35" s="2">
-        <v>880.65</v>
+        <v>4253.30</v>
       </c>
     </row>
     <row r="36" spans="1:2">
@@ -791,7 +791,7 @@
         <v>35</v>
       </c>
       <c r="B36" s="2">
-        <v>8143.07</v>
+        <v>180.10</v>
       </c>
     </row>
     <row r="37" spans="1:2">
@@ -799,7 +799,7 @@
         <v>36</v>
       </c>
       <c r="B37" s="2">
-        <v>1149.80</v>
+        <v>30848.02</v>
       </c>
     </row>
     <row r="38" spans="1:2">
@@ -807,7 +807,7 @@
         <v>37</v>
       </c>
       <c r="B38" s="2">
-        <v>2815.05</v>
+        <v>11696.88</v>
       </c>
     </row>
     <row r="39" spans="1:2">
@@ -815,7 +815,7 @@
         <v>38</v>
       </c>
       <c r="B39" s="2">
-        <v>4253.30</v>
+        <v>3328.39</v>
       </c>
     </row>
     <row r="40" spans="1:2">
@@ -823,7 +823,7 @@
         <v>39</v>
       </c>
       <c r="B40" s="2">
-        <v>180.10</v>
+        <v>2886.37</v>
       </c>
     </row>
   </sheetData>
